--- a/Secure Software Design and Development/Assign/A1/Assign1.xlsx
+++ b/Secure Software Design and Development/Assign/A1/Assign1.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="257">
   <si>
     <t xml:space="preserve">Protocol</t>
   </si>
@@ -31,6 +31,12 @@
     <t xml:space="preserve">Threats(Description)</t>
   </si>
   <si>
+    <t xml:space="preserve">Countermeasures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description</t>
+  </si>
+  <si>
     <t xml:space="preserve">Broder Gateway Protocol(BGP)</t>
   </si>
   <si>
@@ -40,30 +46,408 @@
     <t xml:space="preserve">BGP hijacking occurs when an attacker maliciously advertises false routing information, causing internet traffic to be redirected to unauthorized destinations. If BGP security best practices are not implemented, such as route origin validation (ROV) or BGP prefix filtering, it becomes easier for attackers to hijack BGP routes and potentially intercept or manipulate traffic.</t>
   </si>
   <si>
+    <t xml:space="preserve">Implement RPKI and BGP Route Origin Validation (ROV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPKI verifies the legitimacy of route announcements, while ROV detects and prevents route hijacking.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Route hijacking</t>
   </si>
   <si>
     <t xml:space="preserve">Path validation techniques, such as Border Gateway Protocol (BGP) route validation, aim to prevent route hijacking attacks. However, if the validation process is not robust or if there are vulnerabilities in the underlying protocols, attackers can manipulate routing information and redirect traffic to unauthorized destinations. This can lead to data interception, service disruptions, or unauthorized access to network resources.</t>
   </si>
   <si>
+    <t xml:space="preserve">Use BGP prefix filtering and BGP ROV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prefix filtering ensures acceptance of routes only from known peers, and ROV detects unauthorized route changes.</t>
+  </si>
+  <si>
     <t xml:space="preserve">BGP Protocol Vulnerabilities:</t>
   </si>
   <si>
     <t xml:space="preserve">BGP Protocol Vulnerabilities: BGP (Border Gateway Protocol) is a protocol used to exchange routing information between different networks on the internet. Vulnerabilities in BGP can lead to various security issues, such as route hijacking, unauthorized protocol redistribution, or denial of service attacks targeting routing infrastructure.</t>
   </si>
   <si>
+    <t xml:space="preserve">Regularly update BGP software and follow security best practices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software updates patch known vulnerabilities, while following best practices minimizes exposure to protocol weaknesses.</t>
+  </si>
+  <si>
     <t xml:space="preserve">BGP Flap Damping Abuse</t>
   </si>
   <si>
     <t xml:space="preserve">BGP flap damping is a mechanism used to mitigate the impact of unstable or flapping routes in the BGP protocol. However, attackers can abuse this mechanism by intentionally causing route flapping, leading to excessive route damping and potential disruption of routing paths.</t>
   </si>
   <si>
+    <t xml:space="preserve">Configure BGP flap damping thresholds appropriately and monitor for abnormal behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flap damping suppresses route instability, but misconfiguration or abuse can disrupt legitimate traffic.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unauthorized Protocol Redistribution</t>
   </si>
   <si>
     <t xml:space="preserve">Unauthorized protocol redistribution refers to the unauthorized advertisement or propagation of routing information between different networks using the BGP protocol. Attackers may exploit this vulnerability to redirect or intercept network traffic, leading to potential data breaches or unauthorized access.</t>
   </si>
   <si>
+    <t xml:space="preserve">Implement BGP authentication mechanisms (e.g., MD5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Authentication ensures that only authorized routers can participate in BGP routing, preventing unauthorized protocol redistribution.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGP Speaker Impersonation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An attacker impersonates a legitimate BGP speaker, manipulating routing tables to redirect traffic or perform man-in-the-middle attacks, potentially leading to network downtime or data interception.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use cryptographic authentication (e.g., BGP MD5, BGPsec)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cryptographic authentication ensures that BGP peers are who they claim to be, preventing speaker impersonation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGP Session Reset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intentional or accidental reset of BGP sessions disrupts network connectivity, causing route flapping, route instability, and potential service outages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitor BGP session resets and investigate unusual activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGP session resets can indicate network issues or malicious activity; prompt investigation helps mitigate potential disruptions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGP Session Hijack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An unauthorized entity takes control of a BGP session, intercepting and manipulating routing information to divert traffic or launch man-in-the-middle attacks, compromising data integrity and confidentiality.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employ BGPsec to secure BGP sessions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGPsec provides data origin authentication, data integrity, and replay protection, guarding against session hijacking.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGP Update Spoofing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falsification of BGP update messages allows malicious actors to propagate false routing information, leading to traffic redirection, network congestion, and potential denial-of-service attacks against specific destinations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement BGPsec or use BGP TTL Security Hack to prevent update spoofing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGPsec provides cryptographic verification of routing updates, while TTL Security Hack detects and drops spoofed updates.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGP Session Corruption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corruption of BGP session data disrupts communication between BGP peers, potentially causing route instability, misrouting of traffic, and service degradation across the network.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encrypt BGP sessions using IPsec or TLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encryption protects BGP session data from being corrupted or tampered with by unauthorized parties.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGP Peer Flapping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapid, repeated establishment and teardown of BGP sessions by a peer lead to network instability, increased routing convergence time, and potential denial-of-service conditions, impacting network performance and availability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configure BGP flap damping appropriately and address underlying network issues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flap damping suppresses route instability caused by peer flapping, reducing the impact on BGP routing stability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGP Route Dampening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artificially dampening BGP route advertisements mitigates route flapping but may inadvertently delay convergence, affecting network responsiveness and potentially causing suboptimal routing decisions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjust BGP route dampening parameters based on network conditions and monitor for unintended consequences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Route dampening reduces route instability, but misconfiguration can lead to unintended route suppression and performance issues.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eavesdropping/Interception</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attackers can sniff network traffic to capture sensitive management data transmitted between CMIP clients and servers, especially if strong encryption is not implemented.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encryption protects BGP session data from being intercepted or tampered with by unauthorized parties.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spoofing/Impersonation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malicious actors might impersonate legitimate CMIP management stations to gain unauthorized access to network devices or manipulate their configurations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement cryptographic authentication (e.g., BGP MD5, BGPsec)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cryptographic authentication ensures that BGP peers are who they claim to be, preventing spoofing and impersonation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modification/Tampering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attackers could inject malicious code or alter CMIP messages in transit to disrupt network operations or compromise devices.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use BGPsec to ensure integrity of BGP routing updates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGPsec provides data origin authentication, data integrity, and replay protection, guarding against route tampering and modification.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denial-of-Service (DoS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP servers can be targeted with DoS attacks to overwhelm them and prevent legitimate management operations from being performed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deploy BGP Flowspec for traffic filtering at the network edge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGP Flowspec mitigates DoS attacks by filtering malicious traffic closer to its source, preventing overload of network resources.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Social Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deceptive tactics like phishing emails or pretexting calls can trick authorized personnel into revealing credentials or taking actions that compromise network security.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conduct regular security awareness training for network administrators</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Training helps staff recognize and resist social engineering attempts, reducing the risk of unauthorized access or information disclosure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physical Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unauthorized physical access to management consoles or CMIP-enabled devices can allow attackers to bypass security controls or directly exploit vulnerabilities.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement physical security measures for network infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physical security prevents unauthorized access or tampering with networking equipment, protecting against physical threats.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configuration Errors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Improper configuration of CMIP settings, access control lists (ACLs), or network devices can create security gaps that attackers can exploit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Follow BGP configuration best practices and conduct regular audits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best practices minimize the risk of misconfiguration, while audits identify and rectify configuration errors before they cause issues.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Vulnerabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unpatched vulnerabilities in CMIP software or management applications can be used by attackers to gain unauthorized access or control systems.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regularly update BGP software to patch known vulnerabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timely software updates fix security vulnerabilities and bugs, reducing the risk of exploitation by malicious actors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zero-Day Attacks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previously unknown vulnerabilities (zero-day attacks) can be exploited before patches are available, posing a significant risk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employ intrusion detection and prevention systems (IDPS) and implement strict access controls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDPS can detect and mitigate zero-day attacks, while access controls limit the attack surface and minimize the impact of breaches.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP's Potential for Complexity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The structure and functionality of CMIP can be more complex compared to simpler protocols, increasing the risk of misconfiguration and vulnerabilities.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement proper network management and monitoring tools, and provide staff training</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proper management tools and training help mitigate the complexity of CMIP and ensure its effective operation within the network.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limited Adoption and Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Due to its lower adoption rate compared to SNMP, finding security expertise and support for CMIP may be more challenging.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encourage industry-wide adoption and provide comprehensive support resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Increased adoption fosters ecosystem maturity and support resources help address challenges faced by adopters.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historical Security Concerns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">While CMIP standards have evolved, older implementations might have had weaker security features, potentially leaving them more vulnerable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learn from past incidents, conduct thorough risk assessments, and implement appropriate security measures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyzing historical security incidents helps identify vulnerabilities and implement proactive security measures to prevent recurrence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGP Route Recursion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recursive resolution of BGP routes leads to instability, potential routing loops, and increased convergence time, impacting network performance and potentially causing service disruption or denial-of-service conditions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement route recursion prevention mechanisms and monitor for anomalous routing behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Route recursion prevention mechanisms detect and prevent routing loops, ensuring stable and efficient BGP routing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGP Session Eavesdropping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unauthorized monitoring of BGP session traffic allows attackers to intercept sensitive routing information, potentially leading to route manipulation, traffic interception, or unauthorized access to network resources, compromising confidentiality and integrity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encryption protects BGP session data from being intercepted or eavesdropped by unauthorized parties.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGP Session Replay Attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replay of previously recorded BGP session data allows attackers to resubmit legitimate BGP messages, potentially causing route instability, traffic redirection, or denial-of-service conditions, compromising network availability and performance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employ cryptographic timestamping or sequencing mechanisms in BGP sessions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timestamping or sequencing prevents replay attacks by ensuring that duplicate or out-of-sequence messages are detected and discarded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGP Message Fragmentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breaking BGP messages into smaller fragments for attack disrupts communication between BGP peers, potentially causing route instability, misrouting of traffic, and service degradation across the network.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ensure network infrastructure supports full-size BGP messages and implement fragmentation detection mechanisms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full-size BGP messages prevent fragmentation issues, while detection mechanisms identify and discard fragmented or malformed messages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGP Session Redirection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redirecting BGP session traffic to unauthorized destinations allows attackers to intercept, manipulate, or drop traffic, potentially causing service disruption, traffic interception, or unauthorized access to network resources.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement access control lists (ACLs) or use BGPsec to prevent unauthorized session redirection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACLs restrict access to BGP sessions, while BGPsec ensures session integrity and prevents unauthorized redirection.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGP Session Denial of Service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overloading BGP sessions with excessive traffic or resource exhaustion attacks disrupts communication between BGP peers, causing route instability, increased convergence time, and potential denial-of-service conditions, impacting network availability and performance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGP Message Injection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Injecting unauthorized messages into BGP sessions allows attackers to manipulate routing tables, divert traffic, or launch denial-of-service attacks, compromising network availability, integrity, and confidentiality.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cryptographic authentication ensures that BGP messages are authentic, preventing injection of unauthorized or malicious messages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGP Session Brute Forcing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brute force attack to gain unauthorized access to BGP sessions compromises the confidentiality, integrity, and availability of network resources, potentially leading to traffic interception, route manipulation, or denial-of-service conditions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement rate limiting mechanisms and use strong authentication methods (e.g., BGP MD5, BGPsec)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rate limiting slows down brute-force attempts, while strong authentication methods prevent unauthorized access to BGP sessions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGP Route Attrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gradual erosion or loss of BGP route information due to aging or misconfiguration results in route instability, suboptimal routing, or service disruption, impacting network availability and reachability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement route aggregation and filtering mechanisms to reduce the number of advertised routes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Route aggregation and filtering reduce the size of BGP routing tables, minimizing route attrition and improving network scalability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGP Session Churn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High rate of turnover or instability in BGP sessions leads to increased convergence time, route flapping, and potential denial-of-service conditions, affecting network performance, availability, and reachability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimize BGP configurations and peer relationships, and monitor BGP session stability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimization reduces unnecessary BGP session updates, while monitoring helps identify and address session churn issues.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGP Route Oscillation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapid and repetitive changes in BGP route announcements cause instability, route flapping, and increased convergence time, impacting network performance, availability, and reachability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fine-tune BGP route selection policies and implement route dampening mechanisms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Route selection policies and dampening mechanisms stabilize BGP routing by preventing oscillations and fluctuations in route selection.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">---------------------------------------------------------------------------</t>
+  </si>
+  <si>
     <t xml:space="preserve">Network Basic Input/Output System(NetBIOS)</t>
   </si>
   <si>
@@ -73,7 +457,340 @@
     <t xml:space="preserve">Attackers can spoof WINS responses, tricking clients into resolving NetBIOS names to malicious or incorrect IP addresses, leading to potential data leakage, interception, or unauthorized access.</t>
   </si>
   <si>
+    <t xml:space="preserve">NetBIOS Name Service Spoofing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spoofing NetBIOS name resolution responses allows attackers to redirect traffic to malicious hosts, potentially leading to data interception or service disruption.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Session Hijacking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hijacking established NetBIOS sessions enables unauthorized access to network resources, data interception, or injection of malicious traffic, compromising network security.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Name Table Poisoning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Injection of false NetBIOS name entries into the name table disrupts name resolution, causing traffic redirection, service disruption, or unauthorized access to resources.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Session Enumeration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enumeration of active NetBIOS sessions reveals sensitive information about network resources, potentially aiding attackers in reconnaissance or unauthorized access.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Datagram Service Abuse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abuse of the NetBIOS Datagram Service allows attackers to flood network hosts with unsolicited datagrams, leading to network congestion, denial-of-service, or data interception.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Name Cache Poisoning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poisoning the NetBIOS name cache with false name resolution entries disrupts network communication, potentially causing traffic redirection or denial-of-service conditions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Datagram Spoofing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spoofing NetBIOS datagrams enables attackers to impersonate legitimate hosts, potentially leading to unauthorized access, data interception, or service disruption.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Session Redirection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redirecting NetBIOS session traffic to unauthorized hosts allows attackers to intercept, manipulate, or drop traffic, compromising network confidentiality and integrity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Null Session Exploitation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exploiting null sessions allows unauthorized access to NetBIOS shares, potentially leading to data theft, unauthorized file access, or compromise of sensitive information.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Broadcast Storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generating excessive NetBIOS broadcast traffic floods the network, causing congestion, performance degradation, and potential denial-of-service conditions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Resource Exhaustion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exhaustion of NetBIOS resources, such as session slots or name table entries, leads to denial-of-service conditions, disrupting network connectivity and availability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Password Brute Forcing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brute force attacks against NetBIOS services attempt to gain unauthorized access by guessing passwords, compromising network security and exposing sensitive information.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Share Enumeration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enumeration of NetBIOS shares reveals sensitive information about network resources and potentially exposes vulnerabilities, aiding attackers in unauthorized access.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Session Replay Attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replay of captured NetBIOS sessions allows attackers to impersonate legitimate users or hosts, potentially gaining unauthorized access or performing malicious activities.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Service Fingerprinting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fingerprinting NetBIOS services reveals information about network hosts and their configurations, aiding attackers in reconnaissance and planning of targeted attacks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Name Table Denial of Service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overloading the NetBIOS name table with excessive requests or entries causes denial-of-service conditions, disrupting name resolution and network communication.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Session Eavesdropping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eavesdropping on NetBIOS sessions allows attackers to intercept sensitive data, credentials, or session tokens, compromising confidentiality and integrity of network communication.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Authentication Bypass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bypassing NetBIOS authentication mechanisms enables unauthorized access to network resources, potentially leading to data theft, service disruption, or unauthorized activities.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Name Table Modification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modification of NetBIOS name table entries enables attackers to redirect traffic, impersonate legitimate hosts, or perform man-in-the-middle attacks, compromising network security.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Broadcast Interception</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interception of NetBIOS broadcast traffic allows attackers to gather sensitive information about network hosts, potentially aiding in reconnaissance or targeted attacks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Protocol Downgrade Attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downgrading NetBIOS protocol versions to less secure ones exposes vulnerabilities, potentially enabling unauthorized access, data interception, or compromise of network resources.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Session Tampering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tampering with NetBIOS sessions allows attackers to modify, inject, or delete data, compromising data integrity, confidentiality, and the reliability of network communication.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Name Service Amplification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exploiting NetBIOS name service amplification vulnerabilities allows attackers to generate amplified traffic, leading to network congestion, denial-of-service, or data interception.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Service Misconfiguration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Misconfiguration of NetBIOS services introduces vulnerabilities, potentially enabling unauthorized access, data exposure, or service disruption, compromising network security.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Routing Information Disclosure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disclosure of routing information via NetBIOS services reveals sensitive details about network topology, potentially aiding attackers in reconnaissance or planning of targeted attacks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Session Interruption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intentional interruption of NetBIOS sessions disrupts communication between hosts, potentially causing data loss, service disruption, or denial-of-service conditions across the network.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Password Sniffing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sniffing NetBIOS traffic allows attackers to capture plaintext passwords or authentication tokens, compromising network security and potentially enabling unauthorized access.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Service Impersonation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impersonating legitimate NetBIOS services enables attackers to intercept, manipulate, or block network traffic, potentially leading to data theft, service disruption, or unauthorized access.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetBIOS Port Scanning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanning for open NetBIOS ports allows attackers to identify vulnerable hosts, potentially aiding in reconnaissance or exploitation of security weaknesses, compromising network integrity.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CMIP(Common Management Information Protocol) over TCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Message Injection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Injection of unauthorized CMIP messages into the network may result in the manipulation of managed devices, leading to service disruption, unauthorized configuration changes, or data corruption.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unauthorized CMIP Session Hijacking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hijacking established CMIP sessions allows attackers to gain unauthorized access to management information, potentially leading to the compromise of network infrastructure and sensitive data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Session Replay Attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replay of intercepted CMIP sessions enables attackers to replicate legitimate management actions, potentially causing unauthorized configuration changes, service disruption, or data leakage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Message Modification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modification of CMIP messages in transit allows attackers to alter management commands or responses, potentially leading to misconfiguration, service disruption, or compromise of network security.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Denial-of-Service (DoS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floods of CMIP traffic may overwhelm network resources, causing service degradation or disruption of management operations, potentially impacting the availability and reliability of network services.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Session Eavesdropping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eavesdropping on CMIP sessions allows attackers to intercept sensitive management information, potentially revealing network topology, configuration details, or authentication credentials.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Authentication Bypass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bypassing CMIP authentication mechanisms enables unauthorized access to management functions, potentially allowing attackers to modify network configurations, disrupt services, or steal data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Session Hijacking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hijacking active CMIP sessions enables attackers to assume control over management operations, potentially leading to unauthorized configuration changes, service disruption, or data manipulation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Message Replay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replay of previously captured CMIP messages may result in unintended management actions being executed, potentially causing misconfiguration, service disruption, or compromise of network security.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Service Impersonation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impersonating legitimate CMIP services allows attackers to intercept, modify, or block management traffic, potentially leading to unauthorized configuration changes, service disruption, or data theft.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unauthorized CMIP Service Access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unauthorized access to CMIP services may allow attackers to retrieve sensitive management information, potentially aiding in reconnaissance or exploitation of vulnerabilities in network infrastructure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Protocol Parsing Vulnerabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vulnerabilities in CMIP protocol parsing implementations may be exploited by attackers to execute arbitrary code, trigger denial-of-service conditions, or compromise the security of managed devices.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Service Fingerprinting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fingerprinting CMIP services allows attackers to identify vulnerable management interfaces, potentially aiding in the selection of targets for exploitation or reconnaissance of network infrastructure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Protocol Downgrade Attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downgrading CMIP protocol versions to less secure ones exposes vulnerabilities, potentially enabling unauthorized access, data interception, or compromise of network resources.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Session Interception</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interception of CMIP sessions allows attackers to capture sensitive management information, potentially revealing network configurations, device parameters, or authentication credentials.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Message Spoofing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spoofing CMIP messages allows attackers to impersonate legitimate management entities, potentially leading to unauthorized configuration changes, service disruption, or compromise of network security.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Service Misconfiguration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Misconfiguration of CMIP services introduces vulnerabilities, potentially enabling unauthorized access, data exposure, or service disruption, compromising the security of managed network devices.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Service Redirection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redirecting CMIP service requests to malicious hosts allows attackers to intercept management traffic, potentially leading to unauthorized configuration changes, service disruption, or data theft.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Protocol Evasion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evasion techniques used by attackers may circumvent CMIP protocol inspection or filtering mechanisms, allowing malicious activities to go undetected, potentially compromising network security.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Message Tampering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tampering with CMIP messages enables attackers to modify management commands or responses, potentially leading to misconfiguration, service disruption, or compromise of network infrastructure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Session Manipulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manipulating active CMIP sessions allows attackers to modify management operations, potentially leading to unauthorized configuration changes, service disruption, or compromise of network security.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Traffic Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Protocol Replay Attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replay of previously captured CMIP traffic allows attackers to replicate management actions, potentially causing unauthorized configuration changes, service disruption, or data leakage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Protocol Reflection Attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reflection attacks exploit network devices to amplify and reflect CMIP traffic to targeted hosts, potentially causing network congestion, service disruption, or denial-of-service conditions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIP Protocol Brute Force Attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brute force attacks against CMIP services attempt to gain unauthorized access by guessing passwords or authentication tokens, compromising network security and exposing sensitive information.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://copilot.microsoft.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://chat.openai.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://gemini.google.com/</t>
   </si>
 </sst>
 </file>
@@ -83,11 +800,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -105,11 +823,31 @@
       <family val="0"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b val="true"/>
+      <i val="true"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <i val="true"/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -117,6 +855,37 @@
       <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -172,29 +941,77 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -320,86 +1137,1151 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="41.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="128.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="128.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="31.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="82.35"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="D3" s="8"/>
+      <c r="E3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F3" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+    <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10"/>
+      <c r="B4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
+      <c r="D4" s="8"/>
+      <c r="E4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="F4" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10"/>
+      <c r="B5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="C5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="D5" s="8"/>
+      <c r="E5" s="9" t="s">
         <v>16</v>
       </c>
+      <c r="F5" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10"/>
+      <c r="B6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10"/>
+      <c r="B7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10"/>
+      <c r="B8" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10"/>
+      <c r="B9" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10"/>
+      <c r="B10" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10"/>
+      <c r="B11" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10"/>
+      <c r="B12" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10"/>
+      <c r="B13" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10"/>
+      <c r="B14" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10"/>
+      <c r="B15" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10"/>
+      <c r="B16" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10"/>
+      <c r="B17" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10"/>
+      <c r="B18" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="E18" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10"/>
+      <c r="B19" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10"/>
+      <c r="B20" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" s="8"/>
+      <c r="E20" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10"/>
+      <c r="B21" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="8"/>
+      <c r="E21" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10"/>
+      <c r="B22" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" s="8"/>
+      <c r="E22" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10"/>
+      <c r="B23" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" s="8"/>
+      <c r="E23" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10"/>
+      <c r="B24" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10"/>
+      <c r="B25" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="8"/>
+      <c r="E25" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10"/>
+      <c r="B26" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D26" s="8"/>
+      <c r="E26" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10"/>
+      <c r="B27" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D27" s="8"/>
+      <c r="E27" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="10"/>
+      <c r="B28" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" s="8"/>
+      <c r="E28" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="10"/>
+      <c r="B29" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" s="8"/>
+      <c r="E29" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="10"/>
+      <c r="B30" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D30" s="8"/>
+      <c r="E30" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10"/>
+      <c r="B31" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" s="8"/>
+      <c r="E31" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="10"/>
+      <c r="B32" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" s="8"/>
+      <c r="E32" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="10"/>
+      <c r="B33" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" s="8"/>
+      <c r="E33" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="10"/>
+      <c r="B34" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D34" s="8"/>
+      <c r="E34" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="10"/>
+      <c r="B35" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D35" s="8"/>
+      <c r="E35" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="10"/>
+      <c r="B36" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="D36" s="8"/>
+      <c r="E36" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="10"/>
+      <c r="B37" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="D37" s="8"/>
+      <c r="E37" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="10"/>
+      <c r="B38" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C38" s="15"/>
+    </row>
+    <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="10"/>
+      <c r="B40" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="10"/>
+      <c r="B41" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="10"/>
+      <c r="B42" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="10"/>
+      <c r="B43" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="10"/>
+      <c r="B44" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="10"/>
+      <c r="B45" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="10"/>
+      <c r="B46" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="10"/>
+      <c r="B47" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="10"/>
+      <c r="B48" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="10"/>
+      <c r="B49" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="10"/>
+      <c r="B50" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="10"/>
+      <c r="B51" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="10"/>
+      <c r="B52" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="10"/>
+      <c r="B53" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="10"/>
+      <c r="B54" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="10"/>
+      <c r="B55" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="10"/>
+      <c r="B56" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="10"/>
+      <c r="B57" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="10"/>
+      <c r="B58" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="10"/>
+      <c r="B59" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="10"/>
+      <c r="B60" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="10"/>
+      <c r="B61" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="10"/>
+      <c r="B62" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="10"/>
+      <c r="B63" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="10"/>
+      <c r="B64" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="10"/>
+      <c r="B65" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="10"/>
+      <c r="B66" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="10"/>
+      <c r="B67" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="10"/>
+      <c r="B68" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="10"/>
+      <c r="B69" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="10"/>
+      <c r="B70" s="14"/>
+      <c r="C70" s="15"/>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="10"/>
+      <c r="B71" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C71" s="15"/>
+    </row>
+    <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B72" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="10"/>
+      <c r="B73" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="10"/>
+      <c r="B74" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B75" s="1"/>
+      <c r="A75" s="10"/>
+      <c r="B75" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="10"/>
+      <c r="B76" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="10"/>
+      <c r="B77" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="10"/>
+      <c r="B78" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="10"/>
+      <c r="B79" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="10"/>
+      <c r="B80" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="10"/>
+      <c r="B81" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="10"/>
+      <c r="B82" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="C82" s="13" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="10"/>
+      <c r="B83" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="10"/>
+      <c r="B84" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="10"/>
+      <c r="B85" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="10"/>
+      <c r="B86" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="10"/>
+      <c r="B87" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C87" s="13" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="10"/>
+      <c r="B88" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="C88" s="13" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="10"/>
+      <c r="B89" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="C89" s="13" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="10"/>
+      <c r="B90" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="10"/>
+      <c r="B91" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="10"/>
+      <c r="B92" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="10"/>
+      <c r="B93" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="10"/>
+      <c r="B94" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="10"/>
+      <c r="B95" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="10"/>
+      <c r="B96" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="C96" s="13" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="10"/>
+      <c r="B97" s="17"/>
+      <c r="C97" s="17"/>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="s">
+        <v>256</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
